--- a/실시간조서_템플릿.xlsx
+++ b/실시간조서_템플릿.xlsx
@@ -1,115 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\탱고 시스템\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D418ED4E-9175-450F-84D0-2AEA1B0FA8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="1485" windowWidth="18915" windowHeight="12990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1~50" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1~50" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1~50'!$1:$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>실시간(직접) 위치측량 조서</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 사업명 : </t>
-  </si>
-  <si>
-    <t>측량날짜</t>
-  </si>
-  <si>
-    <t>측점명</t>
-  </si>
-  <si>
-    <t>좌표(GRS80)</t>
-  </si>
-  <si>
-    <t>시설물종류</t>
-  </si>
-  <si>
-    <t>재질</t>
-  </si>
-  <si>
-    <t>관경</t>
-  </si>
-  <si>
-    <t>이격거리</t>
-  </si>
-  <si>
-    <t>심도</t>
-  </si>
-  <si>
-    <t>X(N)</t>
-  </si>
-  <si>
-    <t>Y(E)</t>
-  </si>
-  <si>
-    <t>실시간 측량점</t>
-  </si>
-  <si>
-    <t>공사 후 관로</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="164" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="HY견고딕"/>
+      <charset val="129"/>
+      <family val="1"/>
       <sz val="26"/>
-      <name val="HY견고딕"/>
-      <family val="1"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -178,6 +124,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -276,6 +237,19 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -307,6 +281,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -457,6 +442,28 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -464,124 +471,250 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="56">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -905,220 +1038,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="13.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="8" customWidth="1"/>
+    <col width="13.33203125" customWidth="1" style="27" min="1" max="2"/>
+    <col width="10.77734375" customWidth="1" style="27" min="3" max="3"/>
+    <col width="9.33203125" customWidth="1" style="27" min="4" max="4"/>
+    <col width="9.5546875" customWidth="1" style="27" min="5" max="6"/>
+    <col width="9.109375" customWidth="1" style="9" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="37"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="38"/>
-    </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="30"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="31"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="31"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="31"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="31"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="31"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="31"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="31"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="31"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="32"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
-    </row>
-    <row r="19" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="36" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="1" ht="45" customHeight="1" s="48">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>실시간(직접) 위치측량 조서</t>
+        </is>
+      </c>
+      <c r="B1" s="37" t="n"/>
+      <c r="C1" s="37" t="n"/>
+      <c r="D1" s="37" t="n"/>
+      <c r="E1" s="37" t="n"/>
+      <c r="F1" s="37" t="n"/>
+      <c r="G1" s="38" t="n"/>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="48" thickBot="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 사업명 : </t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+      <c r="G2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="48">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>측량날짜</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>측점명</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="47" t="n"/>
+      <c r="G3" s="53" t="n"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" s="48">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>좌표(GRS80)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>시설물종류</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>재질</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>관경</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>이격거리</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>심도</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" s="48">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>X(N)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Y(E)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" s="48">
+      <c r="A6" s="49" t="n"/>
+      <c r="B6" s="50" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" s="48">
+      <c r="A7" s="51" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="40" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" s="48">
+      <c r="A8" s="33" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="G8" s="54" t="n"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" s="48">
+      <c r="A9" s="34" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="G9" s="54" t="n"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" s="48">
+      <c r="A10" s="34" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="G10" s="54" t="n"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" s="48">
+      <c r="A11" s="34" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="G11" s="54" t="n"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" s="48">
+      <c r="A12" s="34" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="G12" s="54" t="n"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" s="48">
+      <c r="A13" s="34" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="G13" s="54" t="n"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" s="48">
+      <c r="A14" s="34" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="G14" s="54" t="n"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" s="48">
+      <c r="A15" s="34" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="G15" s="54" t="n"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" s="48">
+      <c r="A16" s="34" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="G16" s="54" t="n"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" s="48">
+      <c r="A17" s="34" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="G17" s="54" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="48">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1" s="48" thickBot="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>실시간 측량점</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>공사 후 관로</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" s="48"/>
+    <row r="21" ht="20.1" customHeight="1" s="48"/>
+    <row r="22" ht="20.1" customHeight="1" s="48"/>
+    <row r="23" ht="20.1" customHeight="1" s="48"/>
+    <row r="24" ht="20.1" customHeight="1" s="48"/>
+    <row r="25" ht="20.1" customHeight="1" s="48"/>
+    <row r="26" ht="20.1" customHeight="1" s="48"/>
+    <row r="27" ht="20.1" customHeight="1" s="48"/>
+    <row r="28" ht="20.1" customHeight="1" s="48"/>
+    <row r="29" ht="20.1" customHeight="1" s="48"/>
+    <row r="30" ht="20.1" customHeight="1" s="48"/>
+    <row r="31" ht="20.1" customHeight="1" s="48"/>
+    <row r="32" ht="20.1" customHeight="1" s="48"/>
+    <row r="33" ht="20.1" customHeight="1" s="48"/>
+    <row r="34" ht="20.1" customHeight="1" s="48"/>
+    <row r="35" ht="20.1" customHeight="1" s="48"/>
+    <row r="36" ht="20.1" customHeight="1" s="48" thickBot="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:G1"/>
@@ -1130,15 +1285,9 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.74803149606299213" right="0.39370078740157483" top="0.59055118110236227" bottom="0.55118110236220474" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageMargins left="0.7480314960629921" right="0.3937007874015748" top="0.5905511811023623" bottom="0.5511811023622047" header="0.5118110236220472" footer="0.5118110236220472"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/실시간조서_템플릿.xlsx
+++ b/실시간조서_템플릿.xlsx
@@ -1046,11 +1046,11 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col width="13.33203125" customWidth="1" style="27" min="1" max="2"/>
-    <col width="10.77734375" customWidth="1" style="27" min="3" max="3"/>
-    <col width="9.33203125" customWidth="1" style="27" min="4" max="4"/>
-    <col width="9.5546875" customWidth="1" style="27" min="5" max="6"/>
-    <col width="9.109375" customWidth="1" style="9" min="7" max="7"/>
+    <col width="15.065195" customWidth="1" style="27" min="1" max="2"/>
+    <col width="12.178398" customWidth="1" style="27" min="3" max="3"/>
+    <col width="10.545195" customWidth="1" style="27" min="4" max="4"/>
+    <col width="10.796797" customWidth="1" style="27" min="5" max="6"/>
+    <col width="10.293594" customWidth="1" style="9" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" s="48">

--- a/실시간조서_템플릿.xlsx
+++ b/실시간조서_템플릿.xlsx
@@ -1046,11 +1046,11 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col width="15.065195" customWidth="1" style="27" min="1" max="2"/>
-    <col width="12.178398" customWidth="1" style="27" min="3" max="3"/>
-    <col width="10.545195" customWidth="1" style="27" min="4" max="4"/>
-    <col width="10.796797" customWidth="1" style="27" min="5" max="6"/>
-    <col width="10.293594" customWidth="1" style="9" min="7" max="7"/>
+    <col width="13.998633" customWidth="1" style="27" min="1" max="2"/>
+    <col width="11.316211" customWidth="1" style="27" min="3" max="3"/>
+    <col width="9.798633" customWidth="1" style="27" min="4" max="4"/>
+    <col width="10.032422" customWidth="1" style="27" min="5" max="6"/>
+    <col width="9.564844" customWidth="1" style="9" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" s="48">
@@ -1287,7 +1287,7 @@
     <mergeCell ref="A7:C7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7480314960629921" right="0.3937007874015748" top="0.5905511811023623" bottom="0.5511811023622047" header="0.5118110236220472" footer="0.5118110236220472"/>
+  <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/실시간조서_템플릿.xlsx
+++ b/실시간조서_템플릿.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-27240" yWindow="120" windowWidth="17085" windowHeight="16230" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1~50" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1~50'!$1:$2</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="돋움"/>
       <charset val="129"/>
@@ -46,6 +46,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -55,7 +62,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -142,6 +149,39 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -176,6 +216,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -189,6 +242,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -259,24 +323,63 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -394,14 +497,14 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -411,6 +514,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -446,72 +560,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -523,7 +571,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -554,94 +602,142 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1046,248 +1142,247 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col width="13.998633" customWidth="1" style="27" min="1" max="2"/>
-    <col width="11.316211" customWidth="1" style="27" min="3" max="3"/>
-    <col width="9.798633" customWidth="1" style="27" min="4" max="4"/>
-    <col width="10.032422" customWidth="1" style="27" min="5" max="6"/>
-    <col width="9.564844" customWidth="1" style="9" min="7" max="7"/>
+    <col width="13.33203125" customWidth="1" style="1" min="1" max="2"/>
+    <col width="10.77734375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.33203125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.5546875" customWidth="1" style="1" min="5" max="6"/>
+    <col width="9.109375" customWidth="1" style="9" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" s="48">
-      <c r="A1" s="36" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" s="41">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>실시간(직접) 위치측량 조서</t>
         </is>
       </c>
-      <c r="B1" s="37" t="n"/>
-      <c r="C1" s="37" t="n"/>
-      <c r="D1" s="37" t="n"/>
-      <c r="E1" s="37" t="n"/>
-      <c r="F1" s="37" t="n"/>
-      <c r="G1" s="38" t="n"/>
-    </row>
-    <row r="2" ht="20.1" customHeight="1" s="48" thickBot="1">
+      <c r="B1" s="43" t="n"/>
+      <c r="C1" s="43" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="43" t="n"/>
+      <c r="F1" s="43" t="n"/>
+      <c r="G1" s="44" t="n"/>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="41" thickBot="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> 사업명 : </t>
         </is>
       </c>
-      <c r="B2" s="43" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="25" t="n"/>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" s="48">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="46" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1" s="41">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>실시간 측량점</t>
+        </is>
+      </c>
+      <c r="B3" s="45" t="n"/>
+      <c r="C3" s="67" t="n"/>
+      <c r="D3" s="68" t="inlineStr">
+        <is>
+          <t>공사 후 관로</t>
+        </is>
+      </c>
+      <c r="E3" s="45" t="n"/>
+      <c r="F3" s="45" t="n"/>
+      <c r="G3" s="46" t="n"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" s="41">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>측량날짜</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="46" t="inlineStr">
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="49" t="n"/>
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>측점명</t>
         </is>
       </c>
-      <c r="E3" s="46" t="n"/>
-      <c r="F3" s="47" t="n"/>
-      <c r="G3" s="53" t="n"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" s="48">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="69" t="n"/>
+      <c r="G4" s="49" t="n"/>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" s="41">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>좌표(GRS80)</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>시설물종류</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>재질</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>관경</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>이격거리</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>심도</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="48">
-      <c r="A5" s="41" t="inlineStr">
+    <row r="6" ht="20.1" customHeight="1" s="41">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>X(N)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Y(E)</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="18" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" s="48">
-      <c r="A6" s="49" t="n"/>
-      <c r="B6" s="50" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="17" t="n"/>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" s="48">
-      <c r="A7" s="51" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="52" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="16" t="n"/>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" s="48">
-      <c r="A8" s="33" t="n"/>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="G8" s="54" t="n"/>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" s="48">
-      <c r="A9" s="34" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="G9" s="54" t="n"/>
-    </row>
-    <row r="10" ht="20.1" customHeight="1" s="48">
-      <c r="A10" s="34" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="n"/>
-      <c r="G10" s="54" t="n"/>
-    </row>
-    <row r="11" ht="20.1" customHeight="1" s="48">
-      <c r="A11" s="34" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="G11" s="54" t="n"/>
-    </row>
-    <row r="12" ht="20.1" customHeight="1" s="48">
-      <c r="A12" s="34" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="29" t="n"/>
-      <c r="G12" s="54" t="n"/>
-    </row>
-    <row r="13" ht="20.1" customHeight="1" s="48">
-      <c r="A13" s="34" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="G13" s="54" t="n"/>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" s="48">
-      <c r="A14" s="34" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="G14" s="54" t="n"/>
-    </row>
-    <row r="15" ht="20.1" customHeight="1" s="48">
-      <c r="A15" s="34" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="G15" s="54" t="n"/>
-    </row>
-    <row r="16" ht="20.1" customHeight="1" s="48">
-      <c r="A16" s="34" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="G16" s="54" t="n"/>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" s="48">
-      <c r="A17" s="34" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="G17" s="54" t="n"/>
-    </row>
-    <row r="18" ht="19.5" customHeight="1" s="48">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="55" t="n"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1" s="48" thickBot="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>실시간 측량점</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="45" t="n"/>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>공사 후 관로</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="25" t="n"/>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" s="48"/>
-    <row r="21" ht="20.1" customHeight="1" s="48"/>
-    <row r="22" ht="20.1" customHeight="1" s="48"/>
-    <row r="23" ht="20.1" customHeight="1" s="48"/>
-    <row r="24" ht="20.1" customHeight="1" s="48"/>
-    <row r="25" ht="20.1" customHeight="1" s="48"/>
-    <row r="26" ht="20.1" customHeight="1" s="48"/>
-    <row r="27" ht="20.1" customHeight="1" s="48"/>
-    <row r="28" ht="20.1" customHeight="1" s="48"/>
-    <row r="29" ht="20.1" customHeight="1" s="48"/>
-    <row r="30" ht="20.1" customHeight="1" s="48"/>
-    <row r="31" ht="20.1" customHeight="1" s="48"/>
-    <row r="32" ht="20.1" customHeight="1" s="48"/>
-    <row r="33" ht="20.1" customHeight="1" s="48"/>
-    <row r="34" ht="20.1" customHeight="1" s="48"/>
-    <row r="35" ht="20.1" customHeight="1" s="48"/>
-    <row r="36" ht="20.1" customHeight="1" s="48" thickBot="1"/>
+      <c r="C6" s="50" t="n"/>
+      <c r="D6" s="50" t="n"/>
+      <c r="E6" s="50" t="n"/>
+      <c r="F6" s="50" t="n"/>
+      <c r="G6" s="51" t="n"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" s="41">
+      <c r="A7" s="52" t="n"/>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" s="41">
+      <c r="A8" s="54" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="56" t="n"/>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="58" t="n"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1" s="41">
+      <c r="A9" s="18" t="n"/>
+      <c r="C9" s="59" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="G9" s="59" t="n"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" s="41">
+      <c r="A10" s="60" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="G10" s="59" t="n"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" s="41">
+      <c r="A11" s="60" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="G11" s="59" t="n"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" s="41">
+      <c r="A12" s="60" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="G12" s="59" t="n"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" s="41">
+      <c r="A13" s="60" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="G13" s="59" t="n"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" s="41">
+      <c r="A14" s="60" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="G14" s="59" t="n"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" s="41">
+      <c r="A15" s="60" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="G15" s="59" t="n"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" s="41">
+      <c r="A16" s="60" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="G16" s="59" t="n"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" s="41">
+      <c r="A17" s="60" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="G17" s="59" t="n"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" s="41">
+      <c r="A18" s="60" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="61" t="n"/>
+      <c r="G18" s="59" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="41" thickBot="1">
+      <c r="A19" s="62" t="n"/>
+      <c r="B19" s="63" t="n"/>
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="65" t="n"/>
+      <c r="E19" s="63" t="n"/>
+      <c r="F19" s="63" t="n"/>
+      <c r="G19" s="64" t="n"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" s="41"/>
+    <row r="21" ht="20.1" customHeight="1" s="41"/>
+    <row r="22" ht="20.1" customHeight="1" s="41"/>
+    <row r="23" ht="20.1" customHeight="1" s="41"/>
+    <row r="24" ht="20.1" customHeight="1" s="41"/>
+    <row r="25" ht="20.1" customHeight="1" s="41"/>
+    <row r="26" ht="20.1" customHeight="1" s="41"/>
+    <row r="27" ht="20.1" customHeight="1" s="41"/>
+    <row r="28" ht="20.1" customHeight="1" s="41"/>
+    <row r="29" ht="20.1" customHeight="1" s="41"/>
+    <row r="30" ht="20.1" customHeight="1" s="41"/>
+    <row r="31" ht="20.1" customHeight="1" s="41"/>
+    <row r="32" ht="20.1" customHeight="1" s="41"/>
+    <row r="33" ht="20.1" customHeight="1" s="41"/>
+    <row r="34" ht="20.1" customHeight="1" s="41"/>
+    <row r="35" ht="20.1" customHeight="1" s="41"/>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A9:C19"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="D9:G19"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D8:G18"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="A8:C18"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.2" footer="0.2"/>
+  <pageMargins left="0.7480314960629921" right="0.3937007874015748" top="0.5905511811023623" bottom="0.5511811023622047" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>